--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120286928</v>
+        <v>120286900</v>
       </c>
       <c r="B2" t="n">
-        <v>79643</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535467</v>
+        <v>535452</v>
       </c>
       <c r="R2" t="n">
-        <v>7199914</v>
+        <v>7199904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286969</v>
+        <v>120286880</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535467</v>
+        <v>535436</v>
       </c>
       <c r="R3" t="n">
-        <v>7199914</v>
+        <v>7199897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286904</v>
+        <v>120286939</v>
       </c>
       <c r="B4" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535467</v>
+        <v>535688</v>
       </c>
       <c r="R4" t="n">
-        <v>7199914</v>
+        <v>7199971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286906</v>
+        <v>120286927</v>
       </c>
       <c r="B5" t="n">
-        <v>79608</v>
+        <v>79659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R5" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286825</v>
+        <v>120286926</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79659</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,48 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535688</v>
+        <v>535416</v>
       </c>
       <c r="R6" t="n">
-        <v>7199971</v>
+        <v>7199872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286926</v>
+        <v>120286931</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
+        <v>79589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535416</v>
+        <v>535436</v>
       </c>
       <c r="R7" t="n">
-        <v>7199872</v>
+        <v>7199897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120286880</v>
+        <v>120286983</v>
       </c>
       <c r="B8" t="n">
-        <v>74638</v>
+        <v>96877</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1299,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535436</v>
+        <v>535448</v>
       </c>
       <c r="R8" t="n">
-        <v>7199897</v>
+        <v>7199889</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,6 +1380,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286927</v>
+        <v>120286882</v>
       </c>
       <c r="B9" t="n">
-        <v>79643</v>
+        <v>77479</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535610</v>
+        <v>535611</v>
       </c>
       <c r="R9" t="n">
         <v>7199940</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286898</v>
+        <v>120286825</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1517,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535416</v>
+        <v>535688</v>
       </c>
       <c r="R10" t="n">
-        <v>7199872</v>
+        <v>7199971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286900</v>
+        <v>120286904</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535452</v>
+        <v>535467</v>
       </c>
       <c r="R11" t="n">
-        <v>7199904</v>
+        <v>7199914</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286882</v>
+        <v>120286883</v>
       </c>
       <c r="B12" t="n">
-        <v>77463</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,7 +1755,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535611</v>
+        <v>535610</v>
       </c>
       <c r="R12" t="n">
         <v>7199940</v>
@@ -1807,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286931</v>
+        <v>120286969</v>
       </c>
       <c r="B13" t="n">
-        <v>79573</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535436</v>
+        <v>535467</v>
       </c>
       <c r="R13" t="n">
-        <v>7199897</v>
+        <v>7199914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120286883</v>
+        <v>120286928</v>
       </c>
       <c r="B14" t="n">
-        <v>74638</v>
+        <v>79659</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535610</v>
+        <v>535467</v>
       </c>
       <c r="R14" t="n">
-        <v>7199940</v>
+        <v>7199914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286939</v>
+        <v>120286906</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535688</v>
+        <v>535436</v>
       </c>
       <c r="R15" t="n">
-        <v>7199971</v>
+        <v>7199897</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286983</v>
+        <v>120286898</v>
       </c>
       <c r="B16" t="n">
-        <v>96854</v>
+        <v>79624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,47 +2135,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224361</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535448</v>
+        <v>535416</v>
       </c>
       <c r="R16" t="n">
-        <v>7199889</v>
+        <v>7199872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2207,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286880</v>
+        <v>120286927</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>79659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R3" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286939</v>
+        <v>120286898</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535688</v>
+        <v>535416</v>
       </c>
       <c r="R4" t="n">
-        <v>7199971</v>
+        <v>7199872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286927</v>
+        <v>120286926</v>
       </c>
       <c r="B5" t="n">
         <v>79659</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535610</v>
+        <v>535416</v>
       </c>
       <c r="R5" t="n">
-        <v>7199940</v>
+        <v>7199872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286926</v>
+        <v>120286906</v>
       </c>
       <c r="B6" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535416</v>
+        <v>535436</v>
       </c>
       <c r="R6" t="n">
-        <v>7199872</v>
+        <v>7199897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286931</v>
+        <v>120286939</v>
       </c>
       <c r="B7" t="n">
-        <v>79589</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535436</v>
+        <v>535688</v>
       </c>
       <c r="R7" t="n">
-        <v>7199897</v>
+        <v>7199971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120286983</v>
+        <v>120286880</v>
       </c>
       <c r="B8" t="n">
-        <v>96877</v>
+        <v>74654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,47 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535448</v>
+        <v>535436</v>
       </c>
       <c r="R8" t="n">
-        <v>7199889</v>
+        <v>7199897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,7 +1371,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,17 +1382,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
+          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286882</v>
+        <v>120286825</v>
       </c>
       <c r="B9" t="n">
-        <v>77479</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,34 +1405,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535611</v>
+        <v>535688</v>
       </c>
       <c r="R9" t="n">
-        <v>7199940</v>
+        <v>7199971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,17 +1494,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
+          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286825</v>
+        <v>120286928</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,48 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535688</v>
+        <v>535467</v>
       </c>
       <c r="R10" t="n">
-        <v>7199971</v>
+        <v>7199914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286904</v>
+        <v>120286882</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>77479</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535467</v>
+        <v>535611</v>
       </c>
       <c r="R11" t="n">
-        <v>7199914</v>
+        <v>7199940</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1698,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
+          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1810,17 +1800,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
+          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286969</v>
+        <v>120286983</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>96877</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,38 +1819,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>224361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535467</v>
+        <v>535448</v>
       </c>
       <c r="R13" t="n">
-        <v>7199914</v>
+        <v>7199889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,6 +1900,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120286928</v>
+        <v>120286931</v>
       </c>
       <c r="B14" t="n">
-        <v>79659</v>
+        <v>79589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>229748</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535467</v>
+        <v>535436</v>
       </c>
       <c r="R14" t="n">
-        <v>7199914</v>
+        <v>7199897</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286906</v>
+        <v>120286969</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535436</v>
+        <v>535467</v>
       </c>
       <c r="R15" t="n">
-        <v>7199897</v>
+        <v>7199914</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286898</v>
+        <v>120286904</v>
       </c>
       <c r="B16" t="n">
         <v>79624</v>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535416</v>
+        <v>535467</v>
       </c>
       <c r="R16" t="n">
-        <v>7199872</v>
+        <v>7199914</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286928</v>
+        <v>120286883</v>
       </c>
       <c r="B10" t="n">
-        <v>79659</v>
+        <v>74654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535467</v>
+        <v>535610</v>
       </c>
       <c r="R10" t="n">
-        <v>7199914</v>
+        <v>7199940</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
+          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286882</v>
+        <v>120286928</v>
       </c>
       <c r="B11" t="n">
-        <v>77479</v>
+        <v>79659</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535611</v>
+        <v>535467</v>
       </c>
       <c r="R11" t="n">
-        <v>7199940</v>
+        <v>7199914</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,17 +1698,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
+          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286883</v>
+        <v>120286882</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535610</v>
+        <v>535611</v>
       </c>
       <c r="R12" t="n">
         <v>7199940</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120286900</v>
+        <v>120286927</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535452</v>
+        <v>535610</v>
       </c>
       <c r="R2" t="n">
-        <v>7199904</v>
+        <v>7199940</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286927</v>
+        <v>120286898</v>
       </c>
       <c r="B3" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535610</v>
+        <v>535416</v>
       </c>
       <c r="R3" t="n">
-        <v>7199940</v>
+        <v>7199872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286898</v>
+        <v>120286939</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535416</v>
+        <v>535688</v>
       </c>
       <c r="R4" t="n">
-        <v>7199872</v>
+        <v>7199971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286926</v>
+        <v>120286906</v>
       </c>
       <c r="B5" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535416</v>
+        <v>535436</v>
       </c>
       <c r="R5" t="n">
-        <v>7199872</v>
+        <v>7199897</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286906</v>
+        <v>120286926</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535436</v>
+        <v>535416</v>
       </c>
       <c r="R6" t="n">
-        <v>7199897</v>
+        <v>7199872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286939</v>
+        <v>120286880</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535688</v>
+        <v>535436</v>
       </c>
       <c r="R7" t="n">
-        <v>7199971</v>
+        <v>7199897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120286880</v>
+        <v>120286882</v>
       </c>
       <c r="B8" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535436</v>
+        <v>535611</v>
       </c>
       <c r="R8" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
+          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1494,17 +1494,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
+          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286883</v>
+        <v>120286904</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535610</v>
+        <v>535467</v>
       </c>
       <c r="R10" t="n">
-        <v>7199940</v>
+        <v>7199914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
+          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286928</v>
+        <v>120286983</v>
       </c>
       <c r="B11" t="n">
-        <v>79659</v>
+        <v>96877</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,34 +1619,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>224361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535467</v>
+        <v>535448</v>
       </c>
       <c r="R11" t="n">
-        <v>7199914</v>
+        <v>7199889</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1696,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286882</v>
+        <v>120286900</v>
       </c>
       <c r="B12" t="n">
-        <v>77479</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535611</v>
+        <v>535452</v>
       </c>
       <c r="R12" t="n">
-        <v>7199940</v>
+        <v>7199904</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,17 +1810,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Emmy Reimer, Manne Frih, David Magnusson</t>
+          <t>David Magnusson, Manne Frih, Emmy Reimer, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286983</v>
+        <v>120286969</v>
       </c>
       <c r="B13" t="n">
-        <v>96877</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,47 +1829,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224361</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535448</v>
+        <v>535467</v>
       </c>
       <c r="R13" t="n">
-        <v>7199889</v>
+        <v>7199914</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1901,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120286931</v>
+        <v>120286883</v>
       </c>
       <c r="B14" t="n">
-        <v>79589</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R14" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286969</v>
+        <v>120286928</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>79659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286904</v>
+        <v>120286931</v>
       </c>
       <c r="B16" t="n">
-        <v>79624</v>
+        <v>79589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535467</v>
+        <v>535436</v>
       </c>
       <c r="R16" t="n">
-        <v>7199914</v>
+        <v>7199897</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,6 +2223,122 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120461287</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rörtjärnarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>535752</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7199988</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120286927</v>
+        <v>120286898</v>
       </c>
       <c r="B2" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535610</v>
+        <v>535416</v>
       </c>
       <c r="R2" t="n">
-        <v>7199940</v>
+        <v>7199872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286898</v>
+        <v>120286825</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535416</v>
+        <v>535688</v>
       </c>
       <c r="R3" t="n">
-        <v>7199872</v>
+        <v>7199971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286939</v>
+        <v>120286926</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535688</v>
+        <v>535416</v>
       </c>
       <c r="R4" t="n">
-        <v>7199971</v>
+        <v>7199872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286906</v>
+        <v>120286928</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535436</v>
+        <v>535467</v>
       </c>
       <c r="R5" t="n">
-        <v>7199897</v>
+        <v>7199914</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286926</v>
+        <v>120286927</v>
       </c>
       <c r="B6" t="n">
         <v>79659</v>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535416</v>
+        <v>535610</v>
       </c>
       <c r="R6" t="n">
-        <v>7199872</v>
+        <v>7199940</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286880</v>
+        <v>120286931</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>79589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120286882</v>
+        <v>120286983</v>
       </c>
       <c r="B8" t="n">
-        <v>77479</v>
+        <v>96877</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1309,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>224361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535611</v>
+        <v>535448</v>
       </c>
       <c r="R8" t="n">
-        <v>7199940</v>
+        <v>7199889</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1390,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286825</v>
+        <v>120286969</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,44 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535688</v>
+        <v>535467</v>
       </c>
       <c r="R9" t="n">
-        <v>7199971</v>
+        <v>7199914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286904</v>
+        <v>120286882</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>77479</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535467</v>
+        <v>535611</v>
       </c>
       <c r="R10" t="n">
-        <v>7199914</v>
+        <v>7199940</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286983</v>
+        <v>120286900</v>
       </c>
       <c r="B11" t="n">
-        <v>96877</v>
+        <v>79624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,47 +1625,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224361</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535448</v>
+        <v>535452</v>
       </c>
       <c r="R11" t="n">
-        <v>7199889</v>
+        <v>7199904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,7 +1697,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286900</v>
+        <v>120286906</v>
       </c>
       <c r="B12" t="n">
         <v>79624</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535452</v>
+        <v>535436</v>
       </c>
       <c r="R12" t="n">
-        <v>7199904</v>
+        <v>7199897</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286969</v>
+        <v>120286880</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535467</v>
+        <v>535436</v>
       </c>
       <c r="R13" t="n">
-        <v>7199914</v>
+        <v>7199897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286928</v>
+        <v>120286939</v>
       </c>
       <c r="B15" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535467</v>
+        <v>535688</v>
       </c>
       <c r="R15" t="n">
-        <v>7199914</v>
+        <v>7199971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286931</v>
+        <v>120286904</v>
       </c>
       <c r="B16" t="n">
-        <v>79589</v>
+        <v>79624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535436</v>
+        <v>535467</v>
       </c>
       <c r="R16" t="n">
-        <v>7199897</v>
+        <v>7199914</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120286898</v>
+        <v>120286882</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>77479</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535416</v>
+        <v>535611</v>
       </c>
       <c r="R2" t="n">
-        <v>7199872</v>
+        <v>7199940</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286825</v>
+        <v>120286898</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,44 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535688</v>
+        <v>535416</v>
       </c>
       <c r="R3" t="n">
-        <v>7199971</v>
+        <v>7199872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286926</v>
+        <v>120286900</v>
       </c>
       <c r="B4" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535416</v>
+        <v>535452</v>
       </c>
       <c r="R4" t="n">
-        <v>7199872</v>
+        <v>7199904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286928</v>
+        <v>120286825</v>
       </c>
       <c r="B5" t="n">
-        <v>79659</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +993,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535467</v>
+        <v>535688</v>
       </c>
       <c r="R5" t="n">
-        <v>7199914</v>
+        <v>7199971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286927</v>
+        <v>120286939</v>
       </c>
       <c r="B6" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535610</v>
+        <v>535688</v>
       </c>
       <c r="R6" t="n">
-        <v>7199940</v>
+        <v>7199971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286931</v>
+        <v>120286969</v>
       </c>
       <c r="B7" t="n">
-        <v>79589</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535436</v>
+        <v>535467</v>
       </c>
       <c r="R7" t="n">
-        <v>7199897</v>
+        <v>7199914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286969</v>
+        <v>120286928</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>79659</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286882</v>
+        <v>120286926</v>
       </c>
       <c r="B10" t="n">
-        <v>77479</v>
+        <v>79659</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535611</v>
+        <v>535416</v>
       </c>
       <c r="R10" t="n">
-        <v>7199940</v>
+        <v>7199872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286900</v>
+        <v>120286906</v>
       </c>
       <c r="B11" t="n">
         <v>79624</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535452</v>
+        <v>535436</v>
       </c>
       <c r="R11" t="n">
-        <v>7199904</v>
+        <v>7199897</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286906</v>
+        <v>120286880</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286880</v>
+        <v>120286883</v>
       </c>
       <c r="B13" t="n">
         <v>74654</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R13" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120286883</v>
+        <v>120286904</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535610</v>
+        <v>535467</v>
       </c>
       <c r="R14" t="n">
-        <v>7199940</v>
+        <v>7199914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286939</v>
+        <v>120286927</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535688</v>
+        <v>535610</v>
       </c>
       <c r="R15" t="n">
-        <v>7199971</v>
+        <v>7199940</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286904</v>
+        <v>120286931</v>
       </c>
       <c r="B16" t="n">
-        <v>79624</v>
+        <v>79589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535467</v>
+        <v>535436</v>
       </c>
       <c r="R16" t="n">
-        <v>7199914</v>
+        <v>7199897</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120286882</v>
+        <v>120286928</v>
       </c>
       <c r="B2" t="n">
-        <v>77479</v>
+        <v>79659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535611</v>
+        <v>535467</v>
       </c>
       <c r="R2" t="n">
-        <v>7199940</v>
+        <v>7199914</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286898</v>
+        <v>120286825</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535416</v>
+        <v>535688</v>
       </c>
       <c r="R3" t="n">
-        <v>7199872</v>
+        <v>7199971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286900</v>
+        <v>120286939</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535452</v>
+        <v>535688</v>
       </c>
       <c r="R4" t="n">
-        <v>7199904</v>
+        <v>7199971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286825</v>
+        <v>120286906</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,44 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535688</v>
+        <v>535436</v>
       </c>
       <c r="R5" t="n">
-        <v>7199971</v>
+        <v>7199897</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286939</v>
+        <v>120286904</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535688</v>
+        <v>535467</v>
       </c>
       <c r="R6" t="n">
-        <v>7199971</v>
+        <v>7199914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286969</v>
+        <v>120286900</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535467</v>
+        <v>535452</v>
       </c>
       <c r="R7" t="n">
-        <v>7199914</v>
+        <v>7199904</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120286983</v>
+        <v>120286882</v>
       </c>
       <c r="B8" t="n">
-        <v>96877</v>
+        <v>77479</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,47 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224361</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535448</v>
+        <v>535611</v>
       </c>
       <c r="R8" t="n">
-        <v>7199889</v>
+        <v>7199940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,7 +1381,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1409,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286928</v>
+        <v>120286926</v>
       </c>
       <c r="B9" t="n">
         <v>79659</v>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535467</v>
+        <v>535416</v>
       </c>
       <c r="R9" t="n">
-        <v>7199914</v>
+        <v>7199872</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286926</v>
+        <v>120286931</v>
       </c>
       <c r="B10" t="n">
-        <v>79659</v>
+        <v>79589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>229748</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535416</v>
+        <v>535436</v>
       </c>
       <c r="R10" t="n">
-        <v>7199872</v>
+        <v>7199897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286906</v>
+        <v>120286880</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286880</v>
+        <v>120286883</v>
       </c>
       <c r="B12" t="n">
         <v>74654</v>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R12" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286883</v>
+        <v>120286983</v>
       </c>
       <c r="B13" t="n">
-        <v>74654</v>
+        <v>96877</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,38 +1819,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>224361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535610</v>
+        <v>535448</v>
       </c>
       <c r="R13" t="n">
-        <v>7199940</v>
+        <v>7199889</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,6 +1900,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120286904</v>
+        <v>120286969</v>
       </c>
       <c r="B14" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286927</v>
+        <v>120286898</v>
       </c>
       <c r="B15" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535610</v>
+        <v>535416</v>
       </c>
       <c r="R15" t="n">
-        <v>7199940</v>
+        <v>7199872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286931</v>
+        <v>120286927</v>
       </c>
       <c r="B16" t="n">
-        <v>79589</v>
+        <v>79659</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229748</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R16" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120286928</v>
+        <v>120286939</v>
       </c>
       <c r="B2" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535467</v>
+        <v>535688</v>
       </c>
       <c r="R2" t="n">
-        <v>7199914</v>
+        <v>7199971</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120286825</v>
+        <v>120286883</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,44 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535688</v>
+        <v>535610</v>
       </c>
       <c r="R3" t="n">
-        <v>7199971</v>
+        <v>7199940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120286939</v>
+        <v>120286904</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535688</v>
+        <v>535467</v>
       </c>
       <c r="R4" t="n">
-        <v>7199971</v>
+        <v>7199914</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120286906</v>
+        <v>120286927</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535436</v>
+        <v>535610</v>
       </c>
       <c r="R5" t="n">
-        <v>7199897</v>
+        <v>7199940</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120286904</v>
+        <v>120286926</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>79659</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535467</v>
+        <v>535416</v>
       </c>
       <c r="R6" t="n">
-        <v>7199914</v>
+        <v>7199872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120286900</v>
+        <v>120286969</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535452</v>
+        <v>535467</v>
       </c>
       <c r="R7" t="n">
-        <v>7199904</v>
+        <v>7199914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120286882</v>
+        <v>120286898</v>
       </c>
       <c r="B8" t="n">
-        <v>77479</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535611</v>
+        <v>535416</v>
       </c>
       <c r="R8" t="n">
-        <v>7199940</v>
+        <v>7199872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286926</v>
+        <v>120286882</v>
       </c>
       <c r="B9" t="n">
-        <v>79659</v>
+        <v>77479</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535416</v>
+        <v>535611</v>
       </c>
       <c r="R9" t="n">
-        <v>7199872</v>
+        <v>7199940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286931</v>
+        <v>120286825</v>
       </c>
       <c r="B10" t="n">
-        <v>79589</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,38 +1503,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535436</v>
+        <v>535688</v>
       </c>
       <c r="R10" t="n">
-        <v>7199897</v>
+        <v>7199971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286880</v>
+        <v>120286928</v>
       </c>
       <c r="B11" t="n">
-        <v>74654</v>
+        <v>79659</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535436</v>
+        <v>535467</v>
       </c>
       <c r="R11" t="n">
-        <v>7199897</v>
+        <v>7199914</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120286883</v>
+        <v>120286983</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>96877</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,38 +1717,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>224361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535610</v>
+        <v>535448</v>
       </c>
       <c r="R12" t="n">
-        <v>7199940</v>
+        <v>7199889</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,6 +1798,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1807,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120286983</v>
+        <v>120286906</v>
       </c>
       <c r="B13" t="n">
-        <v>96877</v>
+        <v>79624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,47 +1829,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224361</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535448</v>
+        <v>535436</v>
       </c>
       <c r="R13" t="n">
-        <v>7199889</v>
+        <v>7199897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1901,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120286969</v>
+        <v>120286880</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535467</v>
+        <v>535436</v>
       </c>
       <c r="R14" t="n">
-        <v>7199914</v>
+        <v>7199897</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120286898</v>
+        <v>120286931</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>79589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535416</v>
+        <v>535436</v>
       </c>
       <c r="R15" t="n">
-        <v>7199872</v>
+        <v>7199897</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120286927</v>
+        <v>120286900</v>
       </c>
       <c r="B16" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535610</v>
+        <v>535452</v>
       </c>
       <c r="R16" t="n">
-        <v>7199940</v>
+        <v>7199904</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28662-2024 artfynd.xlsx
+++ b/artfynd/A 28662-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120286882</v>
+        <v>120286825</v>
       </c>
       <c r="B9" t="n">
-        <v>77479</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535611</v>
+        <v>535688</v>
       </c>
       <c r="R9" t="n">
-        <v>7199940</v>
+        <v>7199971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286825</v>
+        <v>120286882</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>77479</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,44 +1517,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Koksikoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535688</v>
+        <v>535611</v>
       </c>
       <c r="R10" t="n">
-        <v>7199971</v>
+        <v>7199940</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
